--- a/test/bank2.xlsx
+++ b/test/bank2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abhiraj Das\Documents\DMSBackend\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E1EA52D4-C933-4E39-A6CD-3D4990475558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D0C4536-5040-4D4E-A0CE-1244C5C53929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,9 +40,6 @@
     <t>branch</t>
   </si>
   <si>
-    <t>State Bank of India</t>
-  </si>
-  <si>
     <t>SBIN0001234</t>
   </si>
   <si>
@@ -59,13 +56,16 @@
   </si>
   <si>
     <t>c:/Users/Abhiraj Das/Documents/book66.xlsx</t>
+  </si>
+  <si>
+    <t>SBI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -77,6 +77,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -442,6 +448,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -463,10 +472,10 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -474,28 +483,29 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C2">
         <v>1234567890</v>
       </c>
       <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/test/bank2.xlsx
+++ b/test/bank2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Abhiraj Das\Documents\DMSBackend\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D0C4536-5040-4D4E-A0CE-1244C5C53929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B46BFDA-6D40-4903-8F15-0B094E3156CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
   <si>
     <t>client_id</t>
   </si>
@@ -40,9 +40,6 @@
     <t>branch</t>
   </si>
   <si>
-    <t>SBIN0001234</t>
-  </si>
-  <si>
     <t>Savings</t>
   </si>
   <si>
@@ -59,6 +56,15 @@
   </si>
   <si>
     <t>SBI</t>
+  </si>
+  <si>
+    <t>SB</t>
+  </si>
+  <si>
+    <t>SBIN0001235</t>
+  </si>
+  <si>
+    <t>C:/Users/Abhiraj Das/Documents/DMSBackend/test/bank2.xlsx</t>
   </si>
 </sst>
 </file>
@@ -446,7 +452,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
@@ -472,10 +478,10 @@
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -483,25 +489,51 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2">
         <v>12</v>
       </c>
-      <c r="C2">
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3">
         <v>1234567890</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
         <v>6</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F3" t="s">
         <v>7</v>
       </c>
-      <c r="F2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" t="s">
-        <v>11</v>
+      <c r="G3" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
